--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BUENO ARENAS ALBACETE BASKET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BUENO ARENAS ALBACETE BASKET.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>44.8554</v>
+        <v>43.1893</v>
       </c>
       <c r="E2" t="n">
-        <v>39.8617</v>
+        <v>26.2985</v>
       </c>
       <c r="F2" t="n">
-        <v>4.9935</v>
+        <v>16.8905</v>
       </c>
       <c r="G2" t="n">
-        <v>39.3881</v>
+        <v>-11.8451</v>
       </c>
       <c r="H2" t="n">
-        <v>35.4851</v>
+        <v>-2.8441</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9028</v>
+        <v>-9.001300000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>48.1456</v>
+        <v>11.7591</v>
       </c>
       <c r="K2" t="n">
-        <v>42.161</v>
+        <v>7.5607</v>
       </c>
       <c r="L2" t="n">
-        <v>5.9846</v>
+        <v>4.198200000000002</v>
       </c>
       <c r="M2" t="n">
-        <v>-8.757299999999999</v>
+        <v>-23.6041</v>
       </c>
       <c r="N2" t="n">
-        <v>-6.6759</v>
+        <v>-10.4043</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.0818</v>
+        <v>-13.1997</v>
       </c>
       <c r="P2" t="n">
-        <v>17.2484</v>
+        <v>30.596</v>
       </c>
       <c r="Q2" t="n">
-        <v>-23.4088</v>
+        <v>-26.0781</v>
       </c>
       <c r="R2" t="n">
-        <v>40.6578</v>
+        <v>56.6743</v>
       </c>
       <c r="S2" t="n">
-        <v>7.2487</v>
+        <v>-9.1159</v>
       </c>
       <c r="T2" t="n">
-        <v>9.5999</v>
+        <v>-8.7347</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.351299999999999</v>
+        <v>-0.3812000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>-19.0301</v>
+        <v>33.5541</v>
       </c>
       <c r="W2" t="n">
-        <v>5.5251</v>
+        <v>49.3525</v>
       </c>
       <c r="X2" t="n">
-        <v>-24.5554</v>
+        <v>-15.7983</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>V. MUÑOZ QUIÑONES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>37.6456</v>
+        <v>37.5278</v>
       </c>
       <c r="E3" t="n">
-        <v>24.0242</v>
+        <v>30.1805</v>
       </c>
       <c r="F3" t="n">
-        <v>13.6214</v>
+        <v>7.346900000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-11.8451</v>
+        <v>39.3881</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.8441</v>
+        <v>35.4851</v>
       </c>
       <c r="I3" t="n">
-        <v>-9.001300000000001</v>
+        <v>3.9028</v>
       </c>
       <c r="J3" t="n">
-        <v>11.7591</v>
+        <v>48.1456</v>
       </c>
       <c r="K3" t="n">
-        <v>7.5607</v>
+        <v>42.161</v>
       </c>
       <c r="L3" t="n">
-        <v>4.198200000000002</v>
+        <v>5.9846</v>
       </c>
       <c r="M3" t="n">
-        <v>-23.6041</v>
+        <v>-8.757299999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.4043</v>
+        <v>-6.6759</v>
       </c>
       <c r="O3" t="n">
-        <v>-13.1997</v>
+        <v>-2.0818</v>
       </c>
       <c r="P3" t="n">
-        <v>30.596</v>
+        <v>17.2484</v>
       </c>
       <c r="Q3" t="n">
-        <v>-26.0781</v>
+        <v>-23.4088</v>
       </c>
       <c r="R3" t="n">
-        <v>56.6743</v>
+        <v>40.6578</v>
       </c>
       <c r="S3" t="n">
-        <v>-14.6593</v>
+        <v>-0.07940000000000041</v>
       </c>
       <c r="T3" t="n">
-        <v>-11.0089</v>
+        <v>-0.08129999999999976</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.6507</v>
+        <v>0.00230000000000008</v>
       </c>
       <c r="V3" t="n">
-        <v>33.5541</v>
+        <v>-19.0301</v>
       </c>
       <c r="W3" t="n">
-        <v>49.3525</v>
+        <v>5.5251</v>
       </c>
       <c r="X3" t="n">
-        <v>-15.7983</v>
+        <v>-24.5554</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>37.4018</v>
+        <v>36.783</v>
       </c>
       <c r="E4" t="n">
-        <v>17.9153</v>
+        <v>25.8847</v>
       </c>
       <c r="F4" t="n">
-        <v>19.4866</v>
+        <v>10.8985</v>
       </c>
       <c r="G4" t="n">
         <v>39.4282</v>
@@ -766,13 +766,13 @@
         <v>51.3354</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.2642</v>
+        <v>-5.882899999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-19.675</v>
+        <v>-11.7056</v>
       </c>
       <c r="U4" t="n">
-        <v>14.4107</v>
+        <v>5.823</v>
       </c>
       <c r="V4" t="n">
         <v>12.2728</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>26.5611</v>
+        <v>21.8308</v>
       </c>
       <c r="E5" t="n">
-        <v>36.0214</v>
+        <v>19.9575</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.4603</v>
+        <v>1.8736</v>
       </c>
       <c r="G5" t="n">
-        <v>11.2371</v>
+        <v>47.6904</v>
       </c>
       <c r="H5" t="n">
-        <v>17.5886</v>
+        <v>25.7356</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.351499999999999</v>
+        <v>21.9547</v>
       </c>
       <c r="J5" t="n">
-        <v>25.9011</v>
+        <v>68.74339999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>20.5208</v>
+        <v>38.4016</v>
       </c>
       <c r="L5" t="n">
-        <v>5.380400000000001</v>
+        <v>30.3417</v>
       </c>
       <c r="M5" t="n">
-        <v>-14.664</v>
+        <v>-21.0532</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.9321</v>
+        <v>-12.6661</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.7319</v>
+        <v>-8.3871</v>
       </c>
       <c r="P5" t="n">
-        <v>4.9282</v>
+        <v>-18.8913</v>
       </c>
       <c r="Q5" t="n">
-        <v>-20.9448</v>
+        <v>-66.11999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>25.873</v>
+        <v>47.2285</v>
       </c>
       <c r="S5" t="n">
-        <v>8.2195</v>
+        <v>-9.5557</v>
       </c>
       <c r="T5" t="n">
-        <v>12.1621</v>
+        <v>-9.252800000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.9425</v>
+        <v>-0.3029000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1764</v>
+        <v>2.5877</v>
       </c>
       <c r="W5" t="n">
-        <v>18.903</v>
+        <v>26.5866</v>
       </c>
       <c r="X5" t="n">
-        <v>-16.7266</v>
+        <v>-23.9991</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>12.8702</v>
+        <v>17.6763</v>
       </c>
       <c r="E6" t="n">
-        <v>12.6389</v>
+        <v>24.3488</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2311999999999999</v>
+        <v>-6.672300000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>47.6904</v>
+        <v>11.2371</v>
       </c>
       <c r="H6" t="n">
-        <v>25.7356</v>
+        <v>17.5886</v>
       </c>
       <c r="I6" t="n">
-        <v>21.9547</v>
+        <v>-6.351499999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>68.74339999999999</v>
+        <v>25.9011</v>
       </c>
       <c r="K6" t="n">
-        <v>38.4016</v>
+        <v>20.5208</v>
       </c>
       <c r="L6" t="n">
-        <v>30.3417</v>
+        <v>5.380400000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-21.0532</v>
+        <v>-14.664</v>
       </c>
       <c r="N6" t="n">
-        <v>-12.6661</v>
+        <v>-2.9321</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.3871</v>
+        <v>-11.7319</v>
       </c>
       <c r="P6" t="n">
-        <v>-18.8913</v>
+        <v>4.9282</v>
       </c>
       <c r="Q6" t="n">
-        <v>-66.11999999999999</v>
+        <v>-20.9448</v>
       </c>
       <c r="R6" t="n">
-        <v>47.2285</v>
+        <v>25.873</v>
       </c>
       <c r="S6" t="n">
-        <v>-18.5164</v>
+        <v>-0.6654</v>
       </c>
       <c r="T6" t="n">
-        <v>-16.5714</v>
+        <v>0.4894999999999998</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.9452</v>
+        <v>-1.1546</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5877</v>
+        <v>2.1764</v>
       </c>
       <c r="W6" t="n">
-        <v>26.5866</v>
+        <v>18.903</v>
       </c>
       <c r="X6" t="n">
-        <v>-23.9991</v>
+        <v>-16.7266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>9.7149</v>
+        <v>8.328900000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>12.9924</v>
+        <v>-13.0645</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.2774</v>
+        <v>21.3936</v>
       </c>
       <c r="G7" t="n">
-        <v>3.256200000000001</v>
+        <v>-16.8644</v>
       </c>
       <c r="H7" t="n">
-        <v>12.0689</v>
+        <v>-21.9977</v>
       </c>
       <c r="I7" t="n">
-        <v>-8.812999999999999</v>
+        <v>5.1332</v>
       </c>
       <c r="J7" t="n">
-        <v>16.7135</v>
+        <v>-1.9199</v>
       </c>
       <c r="K7" t="n">
-        <v>15.0702</v>
+        <v>-13.0478</v>
       </c>
       <c r="L7" t="n">
-        <v>1.642800000000001</v>
+        <v>11.1283</v>
       </c>
       <c r="M7" t="n">
-        <v>-13.4573</v>
+        <v>-14.9449</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.0013</v>
+        <v>-8.9496</v>
       </c>
       <c r="O7" t="n">
-        <v>-10.456</v>
+        <v>-5.9954</v>
       </c>
       <c r="P7" t="n">
-        <v>3.4909</v>
+        <v>9.446</v>
       </c>
       <c r="Q7" t="n">
-        <v>-22.5876</v>
+        <v>-41.0682</v>
       </c>
       <c r="R7" t="n">
-        <v>26.0785</v>
+        <v>50.5142</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2444</v>
+        <v>-16.5551</v>
       </c>
       <c r="T7" t="n">
-        <v>3.739100000000001</v>
+        <v>-11.6583</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5047999999999997</v>
+        <v>-4.8962</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2763</v>
+        <v>32.3028</v>
       </c>
       <c r="W7" t="n">
-        <v>15.127</v>
+        <v>41.5824</v>
       </c>
       <c r="X7" t="n">
-        <v>-16.4031</v>
+        <v>-9.2796</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>3.4434</v>
+        <v>3.8581</v>
       </c>
       <c r="E8" t="n">
-        <v>6.6978</v>
+        <v>6.0692</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2545</v>
+        <v>-2.2108</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1194000000000002</v>
+        <v>3.256200000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0582</v>
+        <v>12.0689</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1775</v>
+        <v>-8.812999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>5.5039</v>
+        <v>16.7135</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3731</v>
+        <v>15.0702</v>
       </c>
       <c r="L8" t="n">
-        <v>2.1307</v>
+        <v>1.642800000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.623200000000001</v>
+        <v>-13.4573</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.3148</v>
+        <v>-3.0013</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.3082</v>
+        <v>-10.456</v>
       </c>
       <c r="P8" t="n">
-        <v>4.7229</v>
+        <v>3.4909</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2587</v>
+        <v>-22.5876</v>
       </c>
       <c r="R8" t="n">
-        <v>6.9816</v>
+        <v>26.0785</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8526999999999999</v>
+        <v>-1.6125</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0954</v>
+        <v>-3.1837</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.243</v>
+        <v>1.5711</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.0127</v>
+        <v>-1.2763</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3573</v>
+        <v>15.127</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.369899999999999</v>
+        <v>-16.4031</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U. DÁMASO GONZÁLEZ</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1395</v>
+        <v>2.6519</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>5.1444</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1395</v>
+        <v>-2.4925</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1395</v>
+        <v>-0.1194000000000002</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1.0582</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1395</v>
+        <v>-1.1775</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>5.5039</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.3731</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.1307</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1395</v>
+        <v>-5.623200000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-2.3148</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1395</v>
+        <v>-3.3082</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.7229</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.2587</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>6.9816</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.06090000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.458</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.5189</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.0127</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-4.369899999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>U. DÁMASO GONZÁLEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.156699999999999</v>
+        <v>0.1395</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1193</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0374</v>
+        <v>0.1395</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5309</v>
+        <v>0.1395</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7939999999999996</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7368999999999997</v>
+        <v>0.1395</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9904</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9124000000000001</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.078</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4595</v>
+        <v>0.1395</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1184000000000001</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3409999999999999</v>
+        <v>0.1395</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2855</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>6.3657</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.2577</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.0377</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.2201</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7153</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.0082</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.7235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.379799999999999</v>
+        <v>-1.6697</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.9932</v>
+        <v>-2.5032</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3867</v>
+        <v>0.8334999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5609</v>
+        <v>1.5309</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2391</v>
+        <v>0.7939999999999996</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7997</v>
+        <v>0.7368999999999997</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6388</v>
+        <v>1.9904</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2827999999999999</v>
+        <v>0.9124000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.9216</v>
+        <v>1.078</v>
       </c>
       <c r="M11" t="n">
-        <v>1.078</v>
+        <v>-0.4595</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9560999999999999</v>
+        <v>-0.1184000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1218000000000001</v>
+        <v>-0.3409999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2587</v>
+        <v>3.2855</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.0801</v>
       </c>
       <c r="R11" t="n">
-        <v>5.3388</v>
+        <v>6.3657</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.481100000000001</v>
+        <v>-3.7707</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.3441</v>
+        <v>-3.4217</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1371</v>
+        <v>-0.349</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.5968</v>
+        <v>-2.7153</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0698</v>
+        <v>2.0082</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.666600000000001</v>
+        <v>-4.7235</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.7729</v>
+        <v>-6.5951</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.1676</v>
+        <v>-6.92</v>
       </c>
       <c r="F12" t="n">
-        <v>6.395099999999999</v>
+        <v>0.3247999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-16.9049</v>
+        <v>-1.5609</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.0828</v>
+        <v>1.2391</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.8222</v>
+        <v>-2.7997</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.8957</v>
+        <v>-2.6388</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4678</v>
+        <v>0.2827999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.363499999999999</v>
+        <v>-2.9216</v>
       </c>
       <c r="M12" t="n">
-        <v>-12.0096</v>
+        <v>1.078</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.550800000000001</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.4587</v>
+        <v>0.1218000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>22.1772</v>
+        <v>2.2587</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.3472</v>
+        <v>-3.0801</v>
       </c>
       <c r="R12" t="n">
-        <v>35.5242</v>
+        <v>5.3388</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.361599999999999</v>
+        <v>-2.6967</v>
       </c>
       <c r="T12" t="n">
-        <v>-9.910299999999999</v>
+        <v>-2.2709</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5483999999999999</v>
+        <v>-0.4257</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.6829</v>
+        <v>-4.5968</v>
       </c>
       <c r="W12" t="n">
-        <v>11.9852</v>
+        <v>1.0698</v>
       </c>
       <c r="X12" t="n">
-        <v>-17.668</v>
+        <v>-5.666600000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.7591</v>
+        <v>-7.6018</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9244</v>
+        <v>-14.6451</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.8347</v>
+        <v>7.043200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.8037</v>
+        <v>-16.9049</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3182</v>
+        <v>-5.0828</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.4854</v>
+        <v>-11.8222</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.3204</v>
+        <v>-4.8957</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3640000000000001</v>
+        <v>2.4678</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.6843</v>
+        <v>-7.363499999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.4834</v>
+        <v>-12.0096</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6825</v>
+        <v>-7.550800000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.801</v>
+        <v>-4.4587</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2853</v>
+        <v>22.1772</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2587</v>
+        <v>-13.3472</v>
       </c>
       <c r="R13" t="n">
-        <v>5.5441</v>
+        <v>35.5242</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6352</v>
+        <v>-7.1907</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9962</v>
+        <v>-8.3874</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.639</v>
+        <v>1.1968</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.605700000000001</v>
+        <v>-5.6829</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3491</v>
+        <v>11.9852</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.256600000000001</v>
+        <v>-17.668</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.5767</v>
+        <v>-10.8896</v>
       </c>
       <c r="E14" t="n">
-        <v>-25.0358</v>
+        <v>-4.8972</v>
       </c>
       <c r="F14" t="n">
-        <v>12.4592</v>
+        <v>-5.9924</v>
       </c>
       <c r="G14" t="n">
-        <v>-16.8644</v>
+        <v>-6.8037</v>
       </c>
       <c r="H14" t="n">
-        <v>-21.9977</v>
+        <v>-0.3182</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1332</v>
+        <v>-6.4854</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.9199</v>
+        <v>-1.3204</v>
       </c>
       <c r="K14" t="n">
-        <v>-13.0478</v>
+        <v>0.3640000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>11.1283</v>
+        <v>-1.6843</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.9449</v>
+        <v>-5.4834</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.9496</v>
+        <v>-0.6825</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.9954</v>
+        <v>-4.801</v>
       </c>
       <c r="P14" t="n">
-        <v>9.446</v>
+        <v>3.2853</v>
       </c>
       <c r="Q14" t="n">
-        <v>-41.0682</v>
+        <v>-2.2587</v>
       </c>
       <c r="R14" t="n">
-        <v>50.5142</v>
+        <v>5.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>-37.4605</v>
+        <v>-1.7659</v>
       </c>
       <c r="T14" t="n">
-        <v>-23.63</v>
+        <v>-0.969</v>
       </c>
       <c r="U14" t="n">
-        <v>-13.8304</v>
+        <v>-0.7968999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>32.3028</v>
+        <v>-5.605700000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>41.5824</v>
+        <v>-0.3491</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.2796</v>
+        <v>-5.256600000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-39.8596</v>
+        <v>-28.1134</v>
       </c>
       <c r="E15" t="n">
-        <v>-41.8057</v>
+        <v>-35.5254</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9458</v>
+        <v>7.4117</v>
       </c>
       <c r="G15" t="n">
         <v>-10.8701</v>
@@ -1624,13 +1624,13 @@
         <v>25.8732</v>
       </c>
       <c r="S15" t="n">
-        <v>-16.8864</v>
+        <v>-5.1404</v>
       </c>
       <c r="T15" t="n">
-        <v>-12.2766</v>
+        <v>-5.9964</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.6099</v>
+        <v>0.8560999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-15.5937</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>86.12710000000006</v>
+        <v>117.116</v>
       </c>
       <c r="E16" t="n">
-        <v>51.10569999999998</v>
+        <v>60.3282</v>
       </c>
       <c r="F16" t="n">
-        <v>35.02129999999999</v>
+        <v>56.7878</v>
       </c>
       <c r="G16" t="n">
         <v>77.70189999999999</v>
@@ -1672,7 +1672,7 @@
         <v>80.65219999999998</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.950799999999999</v>
+        <v>-2.950799999999998</v>
       </c>
       <c r="J16" t="n">
         <v>221.4665</v>
@@ -1687,7 +1687,7 @@
         <v>-143.7653</v>
       </c>
       <c r="N16" t="n">
-        <v>-67.32499999999999</v>
+        <v>-67.325</v>
       </c>
       <c r="O16" t="n">
         <v>-76.44040000000001</v>
@@ -1702,16 +1702,16 @@
         <v>383.9893</v>
       </c>
       <c r="S16" t="n">
-        <v>-94.9571</v>
+        <v>-63.9704</v>
       </c>
       <c r="T16" t="n">
-        <v>-74.8537</v>
+        <v>-65.63030000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-20.1053</v>
+        <v>1.661699999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>26.3803</v>
+        <v>26.38029999999999</v>
       </c>
       <c r="W16" t="n">
         <v>211.4773</v>
